--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32AE5F57-0D77-4365-BBA0-2E191B0C2895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733DF135-AF7A-4981-8F59-0FD4A6C3DB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -723,9 +723,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +817,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -917,17 +917,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF1B31D-A2B0-43BC-A587-8474F3E673D9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>98</v>
       </c>
@@ -940,22 +940,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FEA5EE-1EE6-46E7-A593-CB024A1C58ED}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -968,13 +968,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7719AF-9118-4A60-BF7F-3491DAE91C27}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -982,7 +982,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -998,14 +998,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87197585-6EB4-40DD-9571-6763D8C561B1}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
@@ -1031,7 +1031,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -1065,147 +1065,147 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5D3C4F-7CA4-4B49-99BD-C542C86946E3}">
   <dimension ref="A1:A28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>96</v>
       </c>
@@ -1219,17 +1219,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A1A452-25F2-430A-8358-9CDC08D43509}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -1242,13 +1242,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC13775-FB7E-4A2D-845E-DF647C6681C0}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>63</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>65</v>
       </c>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733DF135-AF7A-4981-8F59-0FD4A6C3DB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75D01D0-0145-48CD-8839-AFAD80B5ACB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -141,9 +141,6 @@
     <t>Buyside</t>
   </si>
   <si>
-    <t>BUS - Business Services</t>
-  </si>
-  <si>
     <t>Dealership &amp; Rental Services</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>Jason Cao</t>
+  </si>
+  <si>
+    <t>Business Services</t>
   </si>
 </sst>
 </file>
@@ -426,9 +426,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -466,7 +466,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -572,7 +572,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -714,7 +714,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -828,85 +828,85 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>33</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" t="s">
         <v>34</v>
       </c>
-      <c r="G2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>40</v>
       </c>
-      <c r="S2" t="s">
-        <v>40</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>41</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>42</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>43</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>45</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD2" t="s">
         <v>46</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -924,12 +924,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -947,17 +947,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -979,15 +979,15 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1007,54 +1007,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1072,142 +1072,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1226,12 +1226,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1250,18 +1250,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75D01D0-0145-48CD-8839-AFAD80B5ACB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2715DFF-8341-4A3A-9135-44650A661A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -189,9 +189,6 @@
     <t>CaoUser</t>
   </si>
   <si>
-    <t>Meissa Lee</t>
-  </si>
-  <si>
     <t>Contact</t>
   </si>
   <si>
@@ -352,6 +349,9 @@
   </si>
   <si>
     <t>Business Services</t>
+  </si>
+  <si>
+    <t>Gemma Hardy</t>
   </si>
 </sst>
 </file>
@@ -828,7 +828,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
@@ -861,13 +861,13 @@
         <v>38</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R2" t="s">
         <v>39</v>
@@ -876,7 +876,7 @@
         <v>39</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U2" t="s">
         <v>40</v>
@@ -897,10 +897,10 @@
         <v>45</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AC2" t="s">
         <v>38</v>
@@ -924,12 +924,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -947,17 +947,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -970,8 +970,8 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -984,10 +984,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1007,28 +1007,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1036,25 +1036,25 @@
         <v>41</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
         <v>57</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>58</v>
-      </c>
-      <c r="D2" t="s">
-        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1072,142 +1072,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1226,12 +1226,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1250,18 +1250,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2715DFF-8341-4A3A-9135-44650A661A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE26E36-553F-4FB6-A078-6D783F843C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
   <si>
     <t>Client</t>
   </si>
@@ -352,6 +352,33 @@
   </si>
   <si>
     <t>Gemma Hardy</t>
+  </si>
+  <si>
+    <t>Charles Hibbs</t>
+  </si>
+  <si>
+    <t>Brandon Vo</t>
+  </si>
+  <si>
+    <t>Eric Rolfes</t>
+  </si>
+  <si>
+    <t>Sean Brant</t>
+  </si>
+  <si>
+    <t>Bennett Tullos</t>
+  </si>
+  <si>
+    <t>Jordan Mendel</t>
+  </si>
+  <si>
+    <t>John McCarthy</t>
+  </si>
+  <si>
+    <t>Lou Schmalen</t>
+  </si>
+  <si>
+    <t>Dudley Baker</t>
   </si>
 </sst>
 </file>
@@ -375,12 +402,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -395,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -408,6 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1064,149 +1098,177 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5D3C4F-7CA4-4B49-99BD-C542C86946E3}">
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>111</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1218,20 +1280,24 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A1A452-25F2-430A-8358-9CDC08D43509}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE26E36-553F-4FB6-A078-6D783F843C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2771F3-C760-435C-B2FF-EABA3C5954F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -385,7 +385,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,19 +401,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -441,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -757,9 +758,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -851,7 +852,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -951,17 +952,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF1B31D-A2B0-43BC-A587-8474F3E673D9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -974,22 +975,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FEA5EE-1EE6-46E7-A593-CB024A1C58ED}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>98</v>
       </c>
@@ -1002,13 +1003,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7719AF-9118-4A60-BF7F-3491DAE91C27}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1016,7 +1017,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1032,14 +1033,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87197585-6EB4-40DD-9571-6763D8C561B1}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>48</v>
       </c>
@@ -1065,7 +1066,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -1099,23 +1100,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5D3C4F-7CA4-4B49-99BD-C542C86946E3}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -1123,7 +1124,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -1131,22 +1132,22 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -1154,32 +1155,33 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="6"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>106</v>
       </c>
@@ -1187,7 +1189,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>107</v>
       </c>
@@ -1195,7 +1197,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>108</v>
       </c>
@@ -1203,12 +1205,13 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="6"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -1216,47 +1219,47 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>110</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -1281,23 +1284,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A1A452-25F2-430A-8358-9CDC08D43509}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="B2" t="s">
-        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1308,13 +1311,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC13775-FB7E-4A2D-845E-DF647C6681C0}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>61</v>
       </c>
@@ -1322,7 +1325,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>63</v>
       </c>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2771F3-C760-435C-B2FF-EABA3C5954F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0B3B9F-B0F7-4A44-8200-1908B80A9C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="113">
   <si>
     <t>Client</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t>Dudley Baker</t>
+  </si>
+  <si>
+    <t>Chris1 Lord1</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -759,6 +762,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
   <dimension ref="A1:AD2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1068,7 +1076,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0B3B9F-B0F7-4A44-8200-1908B80A9C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17762BD5-644F-4919-A457-8CD92702424D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -1165,33 +1165,33 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>75</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>91</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>76</v>
@@ -1215,13 +1215,13 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>78</v>
@@ -1229,47 +1229,47 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>85</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>94</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>94</v>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17762BD5-644F-4919-A457-8CD92702424D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF204B5-EF05-4589-BB78-043952986984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>JobType</t>
   </si>
   <si>
-    <t>IndustryGroup</t>
-  </si>
-  <si>
     <t>Sector</t>
   </si>
   <si>
@@ -348,9 +345,6 @@
     <t>Jason Cao</t>
   </si>
   <si>
-    <t>Business Services</t>
-  </si>
-  <si>
     <t>Gemma Hardy</t>
   </si>
   <si>
@@ -382,6 +376,12 @@
   </si>
   <si>
     <t>Chris1 Lord1</t>
+  </si>
+  <si>
+    <t>IndustryGroup/HLSector</t>
+  </si>
+  <si>
+    <t>CSDN-0000007327</t>
   </si>
 </sst>
 </file>
@@ -779,177 +779,177 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
         <v>33</v>
       </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
         <v>34</v>
       </c>
-      <c r="I2" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>35</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" t="s">
         <v>38</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="U2" t="s">
         <v>39</v>
       </c>
-      <c r="S2" t="s">
-        <v>39</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>41</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>42</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>43</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>44</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD2" t="s">
         <v>45</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -967,12 +967,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -990,17 +990,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1019,18 +1019,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1050,54 +1050,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1116,171 +1116,171 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B9" s="6"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1300,15 +1300,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1327,18 +1327,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF204B5-EF05-4589-BB78-043952986984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B95B42C-E802-4070-8F61-D6A0BA29B870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="112">
   <si>
     <t>Client</t>
   </si>
@@ -373,9 +373,6 @@
   </si>
   <si>
     <t>Dudley Baker</t>
-  </si>
-  <si>
-    <t>Chris1 Lord1</t>
   </si>
   <si>
     <t>IndustryGroup/HLSector</t>
@@ -761,14 +758,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,7 +776,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -860,7 +857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -871,7 +868,7 @@
         <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
@@ -960,17 +957,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF1B31D-A2B0-43BC-A587-8474F3E673D9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -983,22 +980,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FEA5EE-1EE6-46E7-A593-CB024A1C58ED}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1011,13 +1008,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7719AF-9118-4A60-BF7F-3491DAE91C27}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1025,7 +1022,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1041,14 +1038,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87197585-6EB4-40DD-9571-6763D8C561B1}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1074,9 +1071,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -1108,23 +1105,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5D3C4F-7CA4-4B49-99BD-C542C86946E3}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -1132,7 +1129,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>102</v>
       </c>
@@ -1140,22 +1137,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>103</v>
       </c>
@@ -1163,33 +1160,33 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>105</v>
       </c>
@@ -1197,7 +1194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>106</v>
       </c>
@@ -1205,7 +1202,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>76</v>
       </c>
@@ -1213,13 +1210,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>107</v>
       </c>
       <c r="B17" s="6"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1227,47 +1224,47 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>109</v>
       </c>
@@ -1275,7 +1272,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -1292,18 +1289,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A1A452-25F2-430A-8358-9CDC08D43509}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1319,13 +1316,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC13775-FB7E-4A2D-845E-DF647C6681C0}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
@@ -1333,7 +1330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>62</v>
       </c>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B95B42C-E802-4070-8F61-D6A0BA29B870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA2E9C68-701C-4B7B-B6E2-C72FAAF14FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
+    <t>CSDN-0000002536</t>
   </si>
 </sst>
 </file>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5106EC64-877A-407A-87F0-BDFEA40FD3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FF2DDD-EF1A-40DD-86B8-41F9116E6679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -378,7 +378,7 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Brian Miller</t>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -758,15 +758,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
   <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -958,17 +958,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF1B31D-A2B0-43BC-A587-8474F3E673D9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -981,22 +981,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FEA5EE-1EE6-46E7-A593-CB024A1C58ED}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1009,13 +1009,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7719AF-9118-4A60-BF7F-3491DAE91C27}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -1039,14 +1039,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87197585-6EB4-40DD-9571-6763D8C561B1}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1106,23 +1106,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5D3C4F-7CA4-4B49-99BD-C542C86946E3}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -1138,22 +1138,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1161,33 +1161,33 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>76</v>
       </c>
@@ -1211,13 +1211,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>106</v>
       </c>
       <c r="B17" s="6"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1225,47 +1225,47 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -1290,18 +1290,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A1A452-25F2-430A-8358-9CDC08D43509}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1317,13 +1317,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC13775-FB7E-4A2D-845E-DF647C6681C0}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="57.28515625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>62</v>
       </c>

--- a/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
+++ b/TestData/LV_TMTI0055029_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForCFLOBOpportunityEngagement.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91FF2DDD-EF1A-40DD-86B8-41F9116E6679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{491B0851-DD47-4F0E-9E28-EB0FD7D09B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" xr2:uid="{2C05E2F5-3DB9-4FD8-8E59-14E5CD867A79}"/>
   </bookViews>
   <sheets>
-    <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
+    <sheet name="Users" sheetId="2" r:id="rId1"/>
     <sheet name="AppName" sheetId="7" r:id="rId2"/>
     <sheet name="ModuleName" sheetId="8" r:id="rId3"/>
-    <sheet name="Users" sheetId="2" r:id="rId4"/>
+    <sheet name="AddOpportunity" sheetId="1" r:id="rId4"/>
     <sheet name="AddContact" sheetId="3" r:id="rId5"/>
     <sheet name="OppDealTeamMembers" sheetId="4" r:id="rId6"/>
     <sheet name="EngDealTeamMembers" sheetId="6" r:id="rId7"/>
@@ -756,198 +756,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
-  <dimension ref="A1:AD2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7719AF-9118-4A60-BF7F-3491DAE91C27}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="U2" t="s">
-        <v>39</v>
-      </c>
-      <c r="V2" t="s">
-        <v>40</v>
-      </c>
-      <c r="W2" t="s">
-        <v>41</v>
-      </c>
-      <c r="X2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -958,17 +788,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF1B31D-A2B0-43BC-A587-8474F3E673D9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>95</v>
       </c>
@@ -981,22 +811,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FEA5EE-1EE6-46E7-A593-CB024A1C58ED}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>97</v>
       </c>
@@ -1007,28 +837,198 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F7719AF-9118-4A60-BF7F-3491DAE91C27}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1A1FE9-CADD-4FD6-8E73-186E076A589E}">
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="U2" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1039,14 +1039,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87197585-6EB4-40DD-9571-6763D8C561B1}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>47</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1106,23 +1106,23 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5D3C4F-7CA4-4B49-99BD-C542C86946E3}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>101</v>
       </c>
@@ -1138,22 +1138,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>102</v>
       </c>
@@ -1161,33 +1161,33 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>71</v>
       </c>
       <c r="B9" s="6"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>104</v>
       </c>
@@ -1195,7 +1195,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>105</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>76</v>
       </c>
@@ -1211,13 +1211,13 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>106</v>
       </c>
       <c r="B17" s="6"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -1225,47 +1225,47 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>89</v>
       </c>
@@ -1290,18 +1290,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A1A452-25F2-430A-8358-9CDC08D43509}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1317,13 +1317,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC13775-FB7E-4A2D-845E-DF647C6681C0}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.33203125" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="57.28515625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>60</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>62</v>
       </c>
